--- a/output/recall_parsed/the_siren_sub-02_parsed.xlsx
+++ b/output/recall_parsed/the_siren_sub-02_parsed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,12 +417,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>recalled_events</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>recall_in_temporal_order</t>
         </is>
@@ -484,7 +472,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> and the mayor was like that's Jeremy he's a theater major like it's all just and then they come back pretty speechless and one of the kid was like are we gonna write about this because the historians need to know about this there's this one part about the when they were trying to figure out what the facility was they made a plan about day one what they do day two and when they went in they saw this like whole research like facility and they were exploring and they saw this big fish tank with glowing lights and there's a dude inside it looking really pale and opened his eyes so there were kind of creeped out and there's the the speaker that was saying intruder discovered insector blah blah blah and then they fled away and did not talk about it until the next day what else oh yeah before they go in to investigate they the three kids were gossiping about this place and they said how like people go in there never comes out and no one ever talks about the sirens</t>
+          <t xml:space="preserve"> and the mayor was like that's Jeremy he's a theater major like it's all just and then they come back pretty speechless and one of the kid was like are we gonna write about this because the historians need to know about this there's this one part about the when they were trying to figure out what the facility was they made a plan about day one what they do day two and when they went in they saw this like whole research like facility and they were exploring and they saw this big fish tank with glowing lights and there's a dude inside it looking really pale and opened his eyes so there were kind of creeper out and there's the the speaker that was saying intruder discovered inspector blah blah blah and then they fled away and did not talk about it until the next day what else oh yeah before they go in to investigate they the three kids were gossiping about this place and they said how like people go in there never comes out and no one ever talks about the sirens</t>
         </is>
       </c>
     </row>
@@ -492,7 +480,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> and that their water bottles that people who gone in there are probably obsessed with water bottles so although I don't really understand the part with water bottles but yeah that's basically the whole story</t>
+          <t xml:space="preserve"> and that their water bottles that people who gone in there are probably obsessed with water bottles so although I don't really understand the part with water bottles but yeah that's basically the whole story.</t>
         </is>
       </c>
     </row>
